--- a/results/02_taxa_assemblage/WardsClustering/tables/taxa_confidence/site_robustness.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/tables/taxa_confidence/site_robustness.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,26 +473,26 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>004ABC</t>
+          <t>DR-03</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.847936693689849</v>
+        <v>0.8452524630835619</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2905</v>
+        <v>0.2808</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6855</v>
+        <v>0.8186</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4176</v>
+        <v>0.1103</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2679</v>
+        <v>0.7083</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -503,26 +503,26 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>010B</t>
+          <t>DR-10</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>0.886603392782555</v>
+        <v>0.8452524630835619</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4228</v>
+        <v>0.2111</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9911</v>
+        <v>0.7909</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1067</v>
+        <v>0.1763</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8844</v>
+        <v>0.6146</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -533,26 +533,26 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>011A</t>
+          <t>DR-54</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>0.847936693689849</v>
+        <v>0.8452524630835619</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2019</v>
+        <v>0.0094</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6468</v>
+        <v>0.5814</v>
       </c>
       <c r="F4" t="n">
-        <v>0.46</v>
+        <v>0.3254</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1868</v>
+        <v>0.256</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -563,26 +563,26 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>016C</t>
+          <t>DR-163</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>0.847936693689849</v>
+        <v>0.925440028538784</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2365</v>
+        <v>0.3885</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6641</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4453</v>
+        <v>0.0309</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2187</v>
+        <v>0.9691</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -593,26 +593,26 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>026C</t>
+          <t>DR-164</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>0.886603392782555</v>
+        <v>0.925440028538784</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2387</v>
+        <v>0.4513</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9478</v>
+        <v>0.9494</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1701</v>
+        <v>0.0402</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7776</v>
+        <v>0.9092</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -623,26 +623,26 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>030ABC</t>
+          <t>DR-167</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>0.886603392782555</v>
+        <v>0.8452524630835619</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5305</v>
+        <v>0.1664</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9913999999999999</v>
+        <v>0.8162</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1154</v>
+        <v>0.0907</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8761</v>
+        <v>0.7255</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -653,26 +653,26 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>033ABC</t>
+          <t>DR-168</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>0.847936693689849</v>
+        <v>0.925440028538784</v>
       </c>
       <c r="D8" t="n">
-        <v>0.236</v>
+        <v>0.4107</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8149</v>
+        <v>0.9438</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0931</v>
+        <v>0.042</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7217</v>
+        <v>0.9019</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -683,26 +683,26 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>035C</t>
+          <t>DR-175</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>0.886603392782555</v>
+        <v>0.8452524630835619</v>
       </c>
       <c r="D9" t="n">
-        <v>0.364</v>
+        <v>0.0357</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9959</v>
+        <v>0.8125</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1074</v>
+        <v>0.1095</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8885</v>
+        <v>0.703</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -713,26 +713,26 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>036C</t>
+          <t>DR-195</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>0.847936693689849</v>
+        <v>0.8452524630835619</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3921</v>
+        <v>0.2114</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.8144</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0833</v>
+        <v>0.0746</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7247</v>
+        <v>0.7398</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -743,26 +743,26 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>058C</t>
+          <t>DR-197</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>0.886603392782555</v>
+        <v>0.8452524630835619</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5393</v>
+        <v>0.2021</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9919</v>
+        <v>0.8173</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1084</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8835</v>
+        <v>0.7187</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -773,26 +773,26 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>060B</t>
+          <t>DR-202</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>0.886603392782555</v>
+        <v>0.96404592749758</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4932</v>
+        <v>0.5591</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9944</v>
+        <v>0.884</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1023</v>
+        <v>0.1045</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8921</v>
+        <v>0.7795</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -803,26 +803,26 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>064B</t>
+          <t>DR-204</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>0.847936693689849</v>
+        <v>0.925440028538784</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1748</v>
+        <v>0.1685</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6813</v>
+        <v>0.8933</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4036</v>
+        <v>0.1462</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2777</v>
+        <v>0.7471</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -833,26 +833,26 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>066A</t>
+          <t>DR-205</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>0.847936693689849</v>
+        <v>0.96404592749758</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1595</v>
+        <v>0.5743</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6412</v>
+        <v>0.8913</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4612</v>
+        <v>0.114</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1801</v>
+        <v>0.7773</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -863,26 +863,26 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>068B</t>
+          <t>DR-206</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>0.847936693689849</v>
+        <v>0.8452524630835619</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4185</v>
+        <v>-0.065</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8062</v>
+        <v>0.742</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0858</v>
+        <v>0.2676</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7204</v>
+        <v>0.4744</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -893,26 +893,26 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>071B</t>
+          <t>DR-207</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>0.886603392782555</v>
+        <v>0.96404592749758</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3176</v>
+        <v>0.353</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9837</v>
+        <v>0.8300999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1336</v>
+        <v>0.2947</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8501</v>
+        <v>0.5354</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -923,26 +923,26 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>073C</t>
+          <t>DR-208</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>0.847936693689849</v>
+        <v>0.96404592749758</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1763</v>
+        <v>0.5768</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7059</v>
+        <v>0.8941</v>
       </c>
       <c r="F17" t="n">
-        <v>0.07969999999999999</v>
+        <v>0.1251</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6262</v>
+        <v>0.769</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -953,26 +953,26 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>094C</t>
+          <t>DR-209</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>0.886603392782555</v>
+        <v>0.96404592749758</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5745</v>
+        <v>0.5238</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9893</v>
+        <v>0.8828</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1083</v>
+        <v>0.1069</v>
       </c>
       <c r="G18" t="n">
-        <v>0.881</v>
+        <v>0.7759</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -983,26 +983,26 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>109C</t>
+          <t>DR-15</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>0.718546723494759</v>
+        <v>0.8452524630835619</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1618</v>
+        <v>0.0403</v>
       </c>
       <c r="E19" t="n">
-        <v>0.788</v>
+        <v>0.7542</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3017</v>
+        <v>0.2616</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4863</v>
+        <v>0.4926</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1013,26 +1013,26 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>121C</t>
+          <t>DR-17</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C20" t="n">
-        <v>0.847936693689849</v>
+        <v>0.96404592749758</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1139</v>
+        <v>0.5591</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6356000000000001</v>
+        <v>0.8883</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4782</v>
+        <v>0.1102</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1574</v>
+        <v>0.7781</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1043,26 +1043,26 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>122B</t>
+          <t>DR-18</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>0.847936693689849</v>
+        <v>0.8452524630835619</v>
       </c>
       <c r="D21" t="n">
-        <v>0.109</v>
+        <v>0.3056</v>
       </c>
       <c r="E21" t="n">
-        <v>0.62</v>
+        <v>0.8243</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4884</v>
+        <v>0.0858</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1316</v>
+        <v>0.7385</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1073,26 +1073,26 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>125A</t>
+          <t>DR-19</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C22" t="n">
-        <v>0.886603392782555</v>
+        <v>0.96404592749758</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5677</v>
+        <v>0.602</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9898</v>
+        <v>0.8884</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1115</v>
+        <v>0.1079</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8783</v>
+        <v>0.7805</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1103,26 +1103,26 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>133B</t>
+          <t>DR-20</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>3</v>
       </c>
       <c r="C23" t="n">
-        <v>0.718546723494759</v>
+        <v>0.96404592749758</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1883</v>
+        <v>0.5591</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8149</v>
+        <v>0.8909</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2592</v>
+        <v>0.1089</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5557</v>
+        <v>0.7819</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1133,26 +1133,26 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>139B</t>
+          <t>DR-23</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>0.847936693689849</v>
+        <v>0.8452524630835619</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1949</v>
+        <v>-0.2465</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8135</v>
+        <v>0.3773</v>
       </c>
       <c r="F24" t="n">
-        <v>0.102</v>
+        <v>0.6827</v>
       </c>
       <c r="G24" t="n">
-        <v>0.7115</v>
+        <v>-0.3054</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1163,26 +1163,26 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>GL1</t>
+          <t>DR-38</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>0.718546723494759</v>
+        <v>0.8452524630835619</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.0313</v>
+        <v>0.0481</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6991000000000001</v>
+        <v>0.5787</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4119</v>
+        <v>0.3265</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2873</v>
+        <v>0.2522</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1193,26 +1193,26 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>DR-40</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>0.847936693689849</v>
+        <v>0.8452524630835619</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4032</v>
+        <v>0.0951</v>
       </c>
       <c r="E26" t="n">
-        <v>0.7691</v>
+        <v>0.7697000000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2885</v>
+        <v>0.2384</v>
       </c>
       <c r="G26" t="n">
-        <v>0.4806</v>
+        <v>0.5314</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1223,26 +1223,26 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>DR-44</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C27" t="n">
-        <v>0.847936693689849</v>
+        <v>0.96404592749758</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3694</v>
+        <v>0.351</v>
       </c>
       <c r="E27" t="n">
-        <v>0.8109</v>
+        <v>0.6798999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0868</v>
+        <v>0.4351</v>
       </c>
       <c r="G27" t="n">
-        <v>0.724</v>
+        <v>0.2448</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1253,26 +1253,26 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>S18</t>
+          <t>DR-45</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>0.847936693689849</v>
+        <v>0.8452524630835619</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2394</v>
+        <v>0.0139</v>
       </c>
       <c r="E28" t="n">
-        <v>0.8139</v>
+        <v>0.7982</v>
       </c>
       <c r="F28" t="n">
-        <v>0.09180000000000001</v>
+        <v>0.1173</v>
       </c>
       <c r="G28" t="n">
-        <v>0.7221</v>
+        <v>0.6808999999999999</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1283,26 +1283,26 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>DR-48</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C29" t="n">
-        <v>0.847936693689849</v>
+        <v>0.96404592749758</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1017</v>
+        <v>0.5435</v>
       </c>
       <c r="E29" t="n">
-        <v>0.7438</v>
+        <v>0.8929</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1094</v>
+        <v>0.1832</v>
       </c>
       <c r="G29" t="n">
-        <v>0.6343</v>
+        <v>0.7098</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1313,26 +1313,26 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>DR-49</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>0.847936693689849</v>
+        <v>0.8452524630835619</v>
       </c>
       <c r="D30" t="n">
-        <v>0.4355</v>
+        <v>-0.1228</v>
       </c>
       <c r="E30" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.7306</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0914</v>
+        <v>0.2852</v>
       </c>
       <c r="G30" t="n">
-        <v>0.7207</v>
+        <v>0.4455</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1343,26 +1343,26 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>DR-50</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C31" t="n">
-        <v>0.847936693689849</v>
+        <v>0.96404592749758</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3788</v>
+        <v>0.3643</v>
       </c>
       <c r="E31" t="n">
-        <v>0.8119</v>
+        <v>0.8547</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0955</v>
+        <v>0.242</v>
       </c>
       <c r="G31" t="n">
-        <v>0.7164</v>
+        <v>0.6128</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1373,26 +1373,26 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>DR-51</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C32" t="n">
-        <v>0.847936693689849</v>
+        <v>0.96404592749758</v>
       </c>
       <c r="D32" t="n">
-        <v>0.4303</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>0.8179</v>
+        <v>0.8894</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0935</v>
+        <v>0.1105</v>
       </c>
       <c r="G32" t="n">
-        <v>0.7244</v>
+        <v>0.7788</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -1403,26 +1403,26 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>S28</t>
+          <t>DR-53</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C33" t="n">
-        <v>0.847936693689849</v>
+        <v>0.96404592749758</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2038</v>
+        <v>0.593</v>
       </c>
       <c r="E33" t="n">
-        <v>0.8119</v>
+        <v>0.8939</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0887</v>
+        <v>0.1081</v>
       </c>
       <c r="G33" t="n">
-        <v>0.7233000000000001</v>
+        <v>0.7857</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -1433,26 +1433,26 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>S28(5)</t>
+          <t>DR-55</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>3</v>
       </c>
       <c r="C34" t="n">
-        <v>0.718546723494759</v>
+        <v>0.96404592749758</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1559</v>
+        <v>0.4462</v>
       </c>
       <c r="E34" t="n">
-        <v>0.7178</v>
+        <v>0.8488</v>
       </c>
       <c r="F34" t="n">
-        <v>0.2309</v>
+        <v>0.2675</v>
       </c>
       <c r="G34" t="n">
-        <v>0.4869</v>
+        <v>0.5813</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -1463,26 +1463,26 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>DR-56</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>0.847936693689849</v>
+        <v>0.8452524630835619</v>
       </c>
       <c r="D35" t="n">
-        <v>0.4175</v>
+        <v>-0.2638</v>
       </c>
       <c r="E35" t="n">
-        <v>0.8115</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>0.09180000000000001</v>
+        <v>0.3004</v>
       </c>
       <c r="G35" t="n">
-        <v>0.7196</v>
+        <v>0.3613</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -1493,26 +1493,26 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>S37</t>
+          <t>DR-59</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C36" t="n">
-        <v>0.847936693689849</v>
+        <v>0.96404592749758</v>
       </c>
       <c r="D36" t="n">
-        <v>0.3285</v>
+        <v>0.5508</v>
       </c>
       <c r="E36" t="n">
-        <v>0.8147</v>
+        <v>0.9061</v>
       </c>
       <c r="F36" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.1257</v>
       </c>
       <c r="G36" t="n">
-        <v>0.7219</v>
+        <v>0.7804</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -1523,26 +1523,26 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>LSC-09</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>0.847936693689849</v>
+        <v>0.8452524630835619</v>
       </c>
       <c r="D37" t="n">
-        <v>0.3613</v>
+        <v>0.1769</v>
       </c>
       <c r="E37" t="n">
-        <v>0.8072</v>
+        <v>0.7936</v>
       </c>
       <c r="F37" t="n">
-        <v>0.08069999999999999</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="G37" t="n">
-        <v>0.7265</v>
+        <v>0.7187</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -1553,26 +1553,26 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>S39</t>
+          <t>DR-140</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C38" t="n">
-        <v>0.847936693689849</v>
+        <v>0.96404592749758</v>
       </c>
       <c r="D38" t="n">
-        <v>0.2678</v>
+        <v>0.1858</v>
       </c>
       <c r="E38" t="n">
-        <v>0.7668</v>
+        <v>0.6246</v>
       </c>
       <c r="F38" t="n">
-        <v>0.2667</v>
+        <v>0.4913</v>
       </c>
       <c r="G38" t="n">
-        <v>0.5001</v>
+        <v>0.1333</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -1583,26 +1583,26 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>S50</t>
+          <t>LSC-17</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>1</v>
       </c>
       <c r="C39" t="n">
-        <v>0.847936693689849</v>
+        <v>0.8452524630835619</v>
       </c>
       <c r="D39" t="n">
-        <v>0.3143</v>
+        <v>0.1475</v>
       </c>
       <c r="E39" t="n">
-        <v>0.8089</v>
+        <v>0.8238</v>
       </c>
       <c r="F39" t="n">
-        <v>0.1058</v>
+        <v>0.0988</v>
       </c>
       <c r="G39" t="n">
-        <v>0.7030999999999999</v>
+        <v>0.725</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -1613,26 +1613,26 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>S51</t>
+          <t>LSC-24</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>1</v>
       </c>
       <c r="C40" t="n">
-        <v>0.847936693689849</v>
+        <v>0.8452524630835619</v>
       </c>
       <c r="D40" t="n">
-        <v>0.1037</v>
+        <v>0.2104</v>
       </c>
       <c r="E40" t="n">
-        <v>0.6677999999999999</v>
+        <v>0.8185</v>
       </c>
       <c r="F40" t="n">
-        <v>0.4432</v>
+        <v>0.0863</v>
       </c>
       <c r="G40" t="n">
-        <v>0.2246</v>
+        <v>0.7322</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -1643,26 +1643,26 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>S52</t>
+          <t>LSC-53</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C41" t="n">
-        <v>0.718546723494759</v>
+        <v>0.8452524630835619</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1714</v>
+        <v>-0.1252</v>
       </c>
       <c r="E41" t="n">
-        <v>0.7024</v>
+        <v>0.8027</v>
       </c>
       <c r="F41" t="n">
-        <v>0.2664</v>
+        <v>0.1413</v>
       </c>
       <c r="G41" t="n">
-        <v>0.4359</v>
+        <v>0.6614</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -1673,26 +1673,26 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>DR-144</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>0.847936693689849</v>
+        <v>0.8452524630835619</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0935</v>
+        <v>0.2368</v>
       </c>
       <c r="E42" t="n">
-        <v>0.681</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F42" t="n">
-        <v>0.1042</v>
+        <v>0.1597</v>
       </c>
       <c r="G42" t="n">
-        <v>0.5768</v>
+        <v>0.6503</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -1703,268 +1703,28 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>S54</t>
+          <t>DR-157</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>0.718546723494759</v>
+        <v>0.8452524630835619</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.066</v>
+        <v>-0.1229</v>
       </c>
       <c r="E43" t="n">
-        <v>0.5572</v>
+        <v>0.4688</v>
       </c>
       <c r="F43" t="n">
-        <v>0.4249</v>
+        <v>0.6168</v>
       </c>
       <c r="G43" t="n">
-        <v>0.1324</v>
+        <v>-0.148</v>
       </c>
       <c r="H43" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>S65</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>1</v>
-      </c>
-      <c r="C44" t="n">
-        <v>0.847936693689849</v>
-      </c>
-      <c r="D44" t="n">
-        <v>0.3467</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0.8036</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0.0838</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0.7198</v>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>S69</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>3</v>
-      </c>
-      <c r="C45" t="n">
-        <v>0.718546723494759</v>
-      </c>
-      <c r="D45" t="n">
-        <v>0.0428</v>
-      </c>
-      <c r="E45" t="n">
-        <v>0.7883</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0.3196</v>
-      </c>
-      <c r="G45" t="n">
-        <v>0.4687</v>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>S70</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>3</v>
-      </c>
-      <c r="C46" t="n">
-        <v>0.718546723494759</v>
-      </c>
-      <c r="D46" t="n">
-        <v>0.0299</v>
-      </c>
-      <c r="E46" t="n">
-        <v>0.7723</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0.3219</v>
-      </c>
-      <c r="G46" t="n">
-        <v>0.4504</v>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr">
-        <is>
-          <t>S72</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>3</v>
-      </c>
-      <c r="C47" t="n">
-        <v>0.718546723494759</v>
-      </c>
-      <c r="D47" t="n">
-        <v>0.2219</v>
-      </c>
-      <c r="E47" t="n">
-        <v>0.7446</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0.2273</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0.5173</v>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>S74</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>3</v>
-      </c>
-      <c r="C48" t="n">
-        <v>0.718546723494759</v>
-      </c>
-      <c r="D48" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="E48" t="n">
-        <v>0.8227</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0.2406</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0.5821</v>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>S79</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>1</v>
-      </c>
-      <c r="C49" t="n">
-        <v>0.847936693689849</v>
-      </c>
-      <c r="D49" t="n">
-        <v>0.3445</v>
-      </c>
-      <c r="E49" t="n">
-        <v>0.7147</v>
-      </c>
-      <c r="F49" t="n">
-        <v>0.3874</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0.3272</v>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>S8</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>1</v>
-      </c>
-      <c r="C50" t="n">
-        <v>0.847936693689849</v>
-      </c>
-      <c r="D50" t="n">
-        <v>0.3575</v>
-      </c>
-      <c r="E50" t="n">
-        <v>0.8052</v>
-      </c>
-      <c r="F50" t="n">
-        <v>0.07920000000000001</v>
-      </c>
-      <c r="G50" t="n">
-        <v>0.726</v>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>S81</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>1</v>
-      </c>
-      <c r="C51" t="n">
-        <v>0.847936693689849</v>
-      </c>
-      <c r="D51" t="n">
-        <v>0.3168</v>
-      </c>
-      <c r="E51" t="n">
-        <v>0.6819</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0.4178</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0.2641</v>
-      </c>
-      <c r="H51" t="inlineStr">
         <is>
           <t>Core</t>
         </is>

--- a/results/02_taxa_assemblage/WardsClustering/tables/taxa_confidence/site_robustness.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/tables/taxa_confidence/site_robustness.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,19 +480,19 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8452524630835619</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2808</v>
+        <v>0.3202</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8186</v>
+        <v>0.8939</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1103</v>
+        <v>0.0074</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7083</v>
+        <v>0.8865</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -503,26 +503,26 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>DR-10</t>
+          <t>DR-94</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8452524630835619</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2111</v>
+        <v>0.2267</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7909</v>
+        <v>0.8777</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1763</v>
+        <v>0.0303</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6146</v>
+        <v>0.8474</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -533,26 +533,26 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>DR-54</t>
+          <t>DR-103</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8452524630835619</v>
+        <v>0.940958804337006</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0094</v>
+        <v>-0.0713</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5814</v>
+        <v>0.7866</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3254</v>
+        <v>0.3453</v>
       </c>
       <c r="G4" t="n">
-        <v>0.256</v>
+        <v>0.4413</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -563,26 +563,26 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>DR-163</t>
+          <t>SCR-01</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>0.925440028538784</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3885</v>
+        <v>0.2942</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0.895</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0309</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9691</v>
+        <v>0.8867</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -593,26 +593,26 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>DR-164</t>
+          <t>SCR-02</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>0.925440028538784</v>
+        <v>0.940958804337006</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4513</v>
+        <v>0.1115</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9494</v>
+        <v>0.8725000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0402</v>
+        <v>0.0898</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9092</v>
+        <v>0.7827</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -623,26 +623,26 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>DR-167</t>
+          <t>LSC-07</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8452524630835619</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1664</v>
+        <v>-0.1004</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8162</v>
+        <v>0.2041</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0907</v>
+        <v>0.7847</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7255</v>
+        <v>-0.5806</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -653,26 +653,26 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>DR-168</t>
+          <t>DR-125</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>0.925440028538784</v>
+        <v>0.940958804337006</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4107</v>
+        <v>0.1032</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9438</v>
+        <v>0.9091</v>
       </c>
       <c r="F8" t="n">
-        <v>0.042</v>
+        <v>0.161</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9019</v>
+        <v>0.7481</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -683,26 +683,26 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>DR-175</t>
+          <t>LSC-09</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8452524630835619</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0357</v>
+        <v>0.2234</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8125</v>
+        <v>0.8088</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1095</v>
+        <v>0.0672</v>
       </c>
       <c r="G9" t="n">
-        <v>0.703</v>
+        <v>0.7416</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -713,26 +713,26 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>DR-195</t>
+          <t>LSC-12</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8452524630835619</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2114</v>
+        <v>0.1956</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8144</v>
+        <v>0.7721</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0746</v>
+        <v>0.1134</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7398</v>
+        <v>0.6587</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -743,26 +743,26 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>DR-197</t>
+          <t>SCR-04</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8452524630835619</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2021</v>
+        <v>0.444</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8173</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.0075</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7187</v>
+        <v>0.8872</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -773,26 +773,26 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>DR-202</t>
+          <t>SCR-10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>0.96404592749758</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5591</v>
+        <v>0.4431</v>
       </c>
       <c r="E12" t="n">
-        <v>0.884</v>
+        <v>0.8972</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1045</v>
+        <v>0.0073</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7795</v>
+        <v>0.89</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -803,26 +803,26 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>DR-204</t>
+          <t>DR-141</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>0.925440028538784</v>
+        <v>0.940958804337006</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1685</v>
+        <v>0.1635</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8933</v>
+        <v>0.9241</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1462</v>
+        <v>0.1859</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7471</v>
+        <v>0.7382</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -833,26 +833,26 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>DR-205</t>
+          <t>DR-143</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>0.96404592749758</v>
+        <v>0.86598189210379</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5743</v>
+        <v>0.0428</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8913</v>
+        <v>0.7708</v>
       </c>
       <c r="F14" t="n">
-        <v>0.114</v>
+        <v>0.3052</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7773</v>
+        <v>0.4656</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -863,26 +863,26 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>DR-206</t>
+          <t>SCR-11</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8452524630835619</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.065</v>
+        <v>0.449</v>
       </c>
       <c r="E15" t="n">
-        <v>0.742</v>
+        <v>0.8937</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2676</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4744</v>
+        <v>0.8858</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -893,26 +893,26 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>DR-207</t>
+          <t>SCR-14</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>0.96404592749758</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D16" t="n">
-        <v>0.353</v>
+        <v>0.2812</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8300999999999999</v>
+        <v>0.8942</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2947</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5354</v>
+        <v>0.8861</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -923,26 +923,26 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>DR-208</t>
+          <t>SCR-17</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>0.96404592749758</v>
+        <v>0.940958804337006</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5768</v>
+        <v>0.1556</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8941</v>
+        <v>0.9142</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1251</v>
+        <v>0.1014</v>
       </c>
       <c r="G17" t="n">
-        <v>0.769</v>
+        <v>0.8128</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -953,26 +953,26 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>DR-209</t>
+          <t>SCR-18</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>0.96404592749758</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5238</v>
+        <v>0.3595</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8828</v>
+        <v>0.8949</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1069</v>
+        <v>0.008</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7759</v>
+        <v>0.8869</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -983,26 +983,26 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>DR-15</t>
+          <t>SCR-19</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8452524630835619</v>
+        <v>0.940958804337006</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0403</v>
+        <v>0.3168</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7542</v>
+        <v>0.9093</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2616</v>
+        <v>0.0496</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4926</v>
+        <v>0.8597</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1013,26 +1013,26 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>DR-17</t>
+          <t>SCR-20</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>0.96404592749758</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5591</v>
+        <v>0.2357</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8883</v>
+        <v>0.8474</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1102</v>
+        <v>0.0323</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7781</v>
+        <v>0.8151</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1043,26 +1043,26 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>DR-18</t>
+          <t>LSC-14</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8452524630835619</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3056</v>
+        <v>0.1873</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8243</v>
+        <v>0.7983</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0858</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7385</v>
+        <v>0.7060999999999999</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1073,26 +1073,26 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>DR-19</t>
+          <t>LSC-15</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>0.96404592749758</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D22" t="n">
-        <v>0.602</v>
+        <v>0.221</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8884</v>
+        <v>0.8221000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1079</v>
+        <v>0.0599</v>
       </c>
       <c r="G22" t="n">
-        <v>0.7805</v>
+        <v>0.7623</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1103,26 +1103,26 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>DR-20</t>
+          <t>LSC-16</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>0.96404592749758</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5591</v>
+        <v>0.4601</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8909</v>
+        <v>0.8948</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1089</v>
+        <v>0.0071</v>
       </c>
       <c r="G23" t="n">
-        <v>0.7819</v>
+        <v>0.8877</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1133,26 +1133,26 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>DR-23</t>
+          <t>LSC-17</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>0.8452524630835619</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2465</v>
+        <v>0.4298</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3773</v>
+        <v>0.8957000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6827</v>
+        <v>0.0077</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.3054</v>
+        <v>0.8879</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1163,26 +1163,26 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>DR-38</t>
+          <t>LSC-18</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>0.8452524630835619</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0481</v>
+        <v>0.2427</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5787</v>
+        <v>0.8931</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3265</v>
+        <v>0.0083</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2522</v>
+        <v>0.8848</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1193,26 +1193,26 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>DR-40</t>
+          <t>LSC-19</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8452524630835619</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0951</v>
+        <v>0.4728</v>
       </c>
       <c r="E26" t="n">
-        <v>0.7697000000000001</v>
+        <v>0.8951</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2384</v>
+        <v>0.0065</v>
       </c>
       <c r="G26" t="n">
-        <v>0.5314</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1223,26 +1223,26 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>DR-44</t>
+          <t>LSC-22</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>0.96404592749758</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D27" t="n">
-        <v>0.351</v>
+        <v>0.3781</v>
       </c>
       <c r="E27" t="n">
-        <v>0.6798999999999999</v>
+        <v>0.8758</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4351</v>
+        <v>0.0155</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2448</v>
+        <v>0.8602</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1253,26 +1253,26 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>DR-45</t>
+          <t>LSC-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>0.8452524630835619</v>
+        <v>0.86598189210379</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0139</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>0.7982</v>
+        <v>0.9004</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1173</v>
+        <v>0.1176</v>
       </c>
       <c r="G28" t="n">
-        <v>0.6808999999999999</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1283,26 +1283,26 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>DR-48</t>
+          <t>LSC-24</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>0.96404592749758</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5435</v>
+        <v>0.4393</v>
       </c>
       <c r="E29" t="n">
-        <v>0.8929</v>
+        <v>0.8939</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1832</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="G29" t="n">
-        <v>0.7098</v>
+        <v>0.8856000000000001</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1313,26 +1313,26 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>DR-49</t>
+          <t>LSC-25</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8452524630835619</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.1228</v>
+        <v>0.3796</v>
       </c>
       <c r="E30" t="n">
-        <v>0.7306</v>
+        <v>0.891</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2852</v>
+        <v>0.01</v>
       </c>
       <c r="G30" t="n">
-        <v>0.4455</v>
+        <v>0.8809</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1343,26 +1343,26 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>DR-50</t>
+          <t>LSC-26</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>0.96404592749758</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3643</v>
+        <v>0.3991</v>
       </c>
       <c r="E31" t="n">
-        <v>0.8547</v>
+        <v>0.8956</v>
       </c>
       <c r="F31" t="n">
-        <v>0.242</v>
+        <v>0.0086</v>
       </c>
       <c r="G31" t="n">
-        <v>0.6128</v>
+        <v>0.887</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1373,26 +1373,26 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>DR-51</t>
+          <t>LSC-27</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>0.96404592749758</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D32" t="n">
-        <v>0.6225000000000001</v>
+        <v>0.3534</v>
       </c>
       <c r="E32" t="n">
-        <v>0.8894</v>
+        <v>0.8966</v>
       </c>
       <c r="F32" t="n">
-        <v>0.1105</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="G32" t="n">
-        <v>0.7788</v>
+        <v>0.8873</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -1403,26 +1403,26 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>DR-53</t>
+          <t>SCR-06</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>0.96404592749758</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D33" t="n">
-        <v>0.593</v>
+        <v>0.1775</v>
       </c>
       <c r="E33" t="n">
-        <v>0.8939</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1081</v>
+        <v>0.3974</v>
       </c>
       <c r="G33" t="n">
-        <v>0.7857</v>
+        <v>0.1103</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -1433,26 +1433,26 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>DR-55</t>
+          <t>LSC-30</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>0.96404592749758</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D34" t="n">
-        <v>0.4462</v>
+        <v>0.4566</v>
       </c>
       <c r="E34" t="n">
-        <v>0.8488</v>
+        <v>0.8951</v>
       </c>
       <c r="F34" t="n">
-        <v>0.2675</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="G34" t="n">
-        <v>0.5813</v>
+        <v>0.8871</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -1463,26 +1463,26 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>DR-56</t>
+          <t>LSC-32</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>0.8452524630835619</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.2638</v>
+        <v>0.3339</v>
       </c>
       <c r="E35" t="n">
-        <v>0.6618000000000001</v>
+        <v>0.8862</v>
       </c>
       <c r="F35" t="n">
-        <v>0.3004</v>
+        <v>0.0207</v>
       </c>
       <c r="G35" t="n">
-        <v>0.3613</v>
+        <v>0.8655</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -1493,26 +1493,26 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>DR-59</t>
+          <t>LSC-37</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>0.96404592749758</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D36" t="n">
-        <v>0.5508</v>
+        <v>0.4329</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9061</v>
+        <v>0.8959</v>
       </c>
       <c r="F36" t="n">
-        <v>0.1257</v>
+        <v>0.008</v>
       </c>
       <c r="G36" t="n">
-        <v>0.7804</v>
+        <v>0.888</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -1523,26 +1523,26 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>LSC-09</t>
+          <t>LSC-38</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>0.8452524630835619</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1769</v>
+        <v>0.3815</v>
       </c>
       <c r="E37" t="n">
-        <v>0.7936</v>
+        <v>0.8791</v>
       </c>
       <c r="F37" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.013</v>
       </c>
       <c r="G37" t="n">
-        <v>0.7187</v>
+        <v>0.8661</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -1553,26 +1553,26 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>DR-140</t>
+          <t>LSC-39</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C38" t="n">
-        <v>0.96404592749758</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1858</v>
+        <v>0.1483</v>
       </c>
       <c r="E38" t="n">
-        <v>0.6246</v>
+        <v>0.8774</v>
       </c>
       <c r="F38" t="n">
-        <v>0.4913</v>
+        <v>0.0287</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1333</v>
+        <v>0.8487</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -1583,26 +1583,26 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>LSC-17</t>
+          <t>LSC-40</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>0.8452524630835619</v>
+        <v>0.86598189210379</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1475</v>
+        <v>0.2377</v>
       </c>
       <c r="E39" t="n">
-        <v>0.8238</v>
+        <v>0.9488</v>
       </c>
       <c r="F39" t="n">
-        <v>0.0988</v>
+        <v>0.1226</v>
       </c>
       <c r="G39" t="n">
-        <v>0.725</v>
+        <v>0.8262</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -1613,26 +1613,26 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>LSC-24</t>
+          <t>LSC-41</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>1</v>
       </c>
       <c r="C40" t="n">
-        <v>0.8452524630835619</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D40" t="n">
-        <v>0.2104</v>
+        <v>0.1128</v>
       </c>
       <c r="E40" t="n">
-        <v>0.8185</v>
+        <v>0.7423</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0863</v>
+        <v>0.1316</v>
       </c>
       <c r="G40" t="n">
-        <v>0.7322</v>
+        <v>0.6107</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -1643,26 +1643,26 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>LSC-53</t>
+          <t>LSC-42</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>0.8452524630835619</v>
+        <v>0.86598189210379</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.1252</v>
+        <v>0.2019</v>
       </c>
       <c r="E41" t="n">
-        <v>0.8027</v>
+        <v>0.9246</v>
       </c>
       <c r="F41" t="n">
-        <v>0.1413</v>
+        <v>0.2076</v>
       </c>
       <c r="G41" t="n">
-        <v>0.6614</v>
+        <v>0.717</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -1673,26 +1673,26 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>DR-144</t>
+          <t>LSC-43</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C42" t="n">
-        <v>0.8452524630835619</v>
+        <v>0.86598189210379</v>
       </c>
       <c r="D42" t="n">
-        <v>0.2368</v>
+        <v>0.1666</v>
       </c>
       <c r="E42" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.9446</v>
       </c>
       <c r="F42" t="n">
-        <v>0.1597</v>
+        <v>0.1399</v>
       </c>
       <c r="G42" t="n">
-        <v>0.6503</v>
+        <v>0.8047</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -1703,28 +1703,538 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
+          <t>LSC-45</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.988503117170494</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.3913</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.8977000000000001</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.0071</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.8905</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>LSC-47</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>2</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0.86598189210379</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.1806</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.9491000000000001</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.1097</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.8395</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>LSC-48</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>2</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.86598189210379</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.2716</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.9454</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.1199</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.8255</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>LSC-53</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.988503117170494</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.4014</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.896</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.0074</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.8885</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>LSC-55</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.988503117170494</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.2514</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.8607</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.0281</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.8326</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>LSC-56</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.988503117170494</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.3656</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.8922</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.8842</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>LSC-57</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.988503117170494</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.1815</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.6506999999999999</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.3048</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>LSC-58</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.988503117170494</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.1796</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.4981</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.4785</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.0195</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>LSC-59</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>2</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.86598189210379</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.2938</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.9471000000000001</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.1215</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.8256</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>LSC-60</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.988503117170494</v>
+      </c>
+      <c r="D52" t="n">
+        <v>-0.0121</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.3275</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.6505</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-0.323</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>LSC-62</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.988503117170494</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.3733</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.8964</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.0067</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.8897</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>SCR-08</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.988503117170494</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.4304</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.8959</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.8884</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>DR-144</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.988503117170494</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.8983</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.0064</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.8919</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>DR-145</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.988503117170494</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.2897</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.8925</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.0074</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.8851</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>SCR-09</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.988503117170494</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0.4021</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.8931</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.0074</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.8857</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>DR-156</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.988503117170494</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.3886</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.8947000000000001</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.8871</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
           <t>DR-157</t>
         </is>
       </c>
-      <c r="B43" t="n">
-        <v>1</v>
-      </c>
-      <c r="C43" t="n">
-        <v>0.8452524630835619</v>
-      </c>
-      <c r="D43" t="n">
-        <v>-0.1229</v>
-      </c>
-      <c r="E43" t="n">
-        <v>0.4688</v>
-      </c>
-      <c r="F43" t="n">
-        <v>0.6168</v>
-      </c>
-      <c r="G43" t="n">
-        <v>-0.148</v>
-      </c>
-      <c r="H43" t="inlineStr">
+      <c r="B59" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.988503117170494</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.2416</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.8792</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.0237</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.8555</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>DR-159</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.988503117170494</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.8944</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.8868</v>
+      </c>
+      <c r="H60" t="inlineStr">
         <is>
           <t>Core</t>
         </is>

--- a/results/02_taxa_assemblage/WardsClustering/tables/taxa_confidence/site_robustness.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/tables/taxa_confidence/site_robustness.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,19 +480,19 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3202</v>
+        <v>0.3081</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8939</v>
+        <v>0.918</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0074</v>
+        <v>0.1096</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8865</v>
+        <v>0.8084</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,19 +510,19 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2267</v>
+        <v>0.1713</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8777</v>
+        <v>0.755</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0303</v>
+        <v>0.3102</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8474</v>
+        <v>0.4449</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -537,22 +537,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>0.940958804337006</v>
+        <v>0.066</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0713</v>
+        <v>0.1649</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7866</v>
+        <v>0.8179</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3453</v>
+        <v>0.1318</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4413</v>
+        <v>0.6861</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -570,19 +570,19 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2942</v>
+        <v>0.3696</v>
       </c>
       <c r="E5" t="n">
-        <v>0.895</v>
+        <v>0.9246</v>
       </c>
       <c r="F5" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.1079</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8867</v>
+        <v>0.8168</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -600,19 +600,19 @@
         <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>0.940958804337006</v>
+        <v>0.870534508464975</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1115</v>
+        <v>0.1837</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8725000000000001</v>
+        <v>0.8568</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0898</v>
+        <v>0.1485</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7827</v>
+        <v>0.7083</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -627,22 +627,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>0.988503117170494</v>
+        <v>0.066</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1004</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2041</v>
+        <v>0.8075</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7847</v>
+        <v>0.1323</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5806</v>
+        <v>0.6753</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -660,19 +660,19 @@
         <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>0.940958804337006</v>
+        <v>0.870534508464975</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1032</v>
+        <v>0.1285</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9091</v>
+        <v>0.7402</v>
       </c>
       <c r="F8" t="n">
-        <v>0.161</v>
+        <v>0.2036</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7481</v>
+        <v>0.5366</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -690,19 +690,19 @@
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2234</v>
+        <v>0.1088</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8088</v>
+        <v>0.6993</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0672</v>
+        <v>0.3244</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7416</v>
+        <v>0.375</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -717,22 +717,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>0.988503117170494</v>
+        <v>0.066</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1956</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7721</v>
+        <v>0.3674</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1134</v>
+        <v>0.6168</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6587</v>
+        <v>-0.2494</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -750,19 +750,19 @@
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D11" t="n">
-        <v>0.444</v>
+        <v>0.4638</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8947000000000001</v>
+        <v>0.9247</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0075</v>
+        <v>0.111</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8872</v>
+        <v>0.8136</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -780,19 +780,19 @@
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4431</v>
+        <v>0.4503</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8972</v>
+        <v>0.9255</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0073</v>
+        <v>0.107</v>
       </c>
       <c r="G12" t="n">
-        <v>0.89</v>
+        <v>0.8185</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -803,26 +803,26 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>DR-141</t>
+          <t>DR-143</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>0.940958804337006</v>
+        <v>0.066</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1635</v>
+        <v>0.0164</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9241</v>
+        <v>0.5613</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1859</v>
+        <v>0.3262</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7382</v>
+        <v>0.2351</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -833,26 +833,26 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>DR-143</t>
+          <t>SCR-11</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>0.86598189210379</v>
+        <v>0.09</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0428</v>
+        <v>0.4816</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7708</v>
+        <v>0.9231</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3052</v>
+        <v>0.1101</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4656</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -863,26 +863,26 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>SCR-11</t>
+          <t>SCR-14</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D15" t="n">
-        <v>0.449</v>
+        <v>0.2649</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8937</v>
+        <v>0.9248</v>
       </c>
       <c r="F15" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.1166</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8858</v>
+        <v>0.8082</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -893,26 +893,26 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>SCR-14</t>
+          <t>SCR-17</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>0.988503117170494</v>
+        <v>0.870534508464975</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2812</v>
+        <v>0.1831</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8942</v>
+        <v>0.8425</v>
       </c>
       <c r="F16" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.1477</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8861</v>
+        <v>0.6948</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -923,26 +923,26 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>SCR-17</t>
+          <t>SCR-18</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>0.940958804337006</v>
+        <v>0.09</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1556</v>
+        <v>0.3454</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9142</v>
+        <v>0.926</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1014</v>
+        <v>0.1128</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8128</v>
+        <v>0.8132</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -953,26 +953,26 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>SCR-18</t>
+          <t>SCR-19</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>0.988503117170494</v>
+        <v>0.870534508464975</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3595</v>
+        <v>0.3525</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8949</v>
+        <v>0.8466</v>
       </c>
       <c r="F18" t="n">
-        <v>0.008</v>
+        <v>0.0456</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8869</v>
+        <v>0.801</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -983,26 +983,26 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>SCR-19</t>
+          <t>SCR-20</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>0.940958804337006</v>
+        <v>0.09</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3168</v>
+        <v>0.2344</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9093</v>
+        <v>0.8711</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0496</v>
+        <v>0.145</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8597</v>
+        <v>0.7261</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1013,26 +1013,26 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>SCR-20</t>
+          <t>LSC-14</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2357</v>
+        <v>0.1969</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8474</v>
+        <v>0.7502</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0323</v>
+        <v>0.2754</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8151</v>
+        <v>0.4748</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1043,26 +1043,26 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>LSC-14</t>
+          <t>LSC-15</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1873</v>
+        <v>0.208</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7983</v>
+        <v>0.7749</v>
       </c>
       <c r="F21" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.264</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7060999999999999</v>
+        <v>0.5109</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1073,26 +1073,26 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>LSC-15</t>
+          <t>LSC-16</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D22" t="n">
-        <v>0.221</v>
+        <v>0.4761</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8221000000000001</v>
+        <v>0.9179</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0599</v>
+        <v>0.1049</v>
       </c>
       <c r="G22" t="n">
-        <v>0.7623</v>
+        <v>0.8131</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1103,26 +1103,26 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>LSC-16</t>
+          <t>LSC-17</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4601</v>
+        <v>0.4605</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8948</v>
+        <v>0.9241</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0071</v>
+        <v>0.1074</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8877</v>
+        <v>0.8167</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1133,26 +1133,26 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>LSC-17</t>
+          <t>LSC-18</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4298</v>
+        <v>0.2554</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8957000000000001</v>
+        <v>0.9127999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0077</v>
+        <v>0.118</v>
       </c>
       <c r="G24" t="n">
-        <v>0.8879</v>
+        <v>0.7948</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1163,26 +1163,26 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>LSC-18</t>
+          <t>LSC-19</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2427</v>
+        <v>0.4989</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8931</v>
+        <v>0.9221</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0083</v>
+        <v>0.1073</v>
       </c>
       <c r="G25" t="n">
-        <v>0.8848</v>
+        <v>0.8148</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1193,26 +1193,26 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>LSC-19</t>
+          <t>LSC-22</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4728</v>
+        <v>0.3386</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8951</v>
+        <v>0.8368</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0065</v>
+        <v>0.218</v>
       </c>
       <c r="G26" t="n">
-        <v>0.8885999999999999</v>
+        <v>0.6188</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1223,26 +1223,26 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>LSC-22</t>
+          <t>LSC-23</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>0.988503117170494</v>
+        <v>0.066</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3781</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>0.8758</v>
+        <v>0.8027</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0155</v>
+        <v>0.1378</v>
       </c>
       <c r="G27" t="n">
-        <v>0.8602</v>
+        <v>0.6649</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1253,26 +1253,26 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>LSC-23</t>
+          <t>LSC-24</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>0.86598189210379</v>
+        <v>0.09</v>
       </c>
       <c r="D28" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.4497</v>
       </c>
       <c r="E28" t="n">
-        <v>0.9004</v>
+        <v>0.9219000000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1176</v>
+        <v>0.1022</v>
       </c>
       <c r="G28" t="n">
-        <v>0.7828000000000001</v>
+        <v>0.8197</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1283,26 +1283,26 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>LSC-24</t>
+          <t>LSC-25</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4393</v>
+        <v>0.3727</v>
       </c>
       <c r="E29" t="n">
-        <v>0.8939</v>
+        <v>0.9131</v>
       </c>
       <c r="F29" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.1236</v>
       </c>
       <c r="G29" t="n">
-        <v>0.8856000000000001</v>
+        <v>0.7895</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1313,26 +1313,26 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>LSC-25</t>
+          <t>LSC-26</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3796</v>
+        <v>0.4094</v>
       </c>
       <c r="E30" t="n">
-        <v>0.891</v>
+        <v>0.9155</v>
       </c>
       <c r="F30" t="n">
-        <v>0.01</v>
+        <v>0.1222</v>
       </c>
       <c r="G30" t="n">
-        <v>0.8809</v>
+        <v>0.7933</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1343,26 +1343,26 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>LSC-26</t>
+          <t>LSC-27</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3991</v>
+        <v>0.3314</v>
       </c>
       <c r="E31" t="n">
-        <v>0.8956</v>
+        <v>0.9214</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0086</v>
+        <v>0.1147</v>
       </c>
       <c r="G31" t="n">
-        <v>0.887</v>
+        <v>0.8067</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1373,26 +1373,26 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>LSC-27</t>
+          <t>SCR-06</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C32" t="n">
-        <v>0.988503117170494</v>
+        <v>0.870534508464975</v>
       </c>
       <c r="D32" t="n">
-        <v>0.3534</v>
+        <v>-0.1492</v>
       </c>
       <c r="E32" t="n">
-        <v>0.8966</v>
+        <v>0.5443</v>
       </c>
       <c r="F32" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.368</v>
       </c>
       <c r="G32" t="n">
-        <v>0.8873</v>
+        <v>0.1763</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -1403,26 +1403,26 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>SCR-06</t>
+          <t>LSC-37</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1775</v>
+        <v>0.4694</v>
       </c>
       <c r="E33" t="n">
-        <v>0.5076000000000001</v>
+        <v>0.9225</v>
       </c>
       <c r="F33" t="n">
-        <v>0.3974</v>
+        <v>0.1061</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1103</v>
+        <v>0.8164</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -1433,26 +1433,26 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>LSC-30</t>
+          <t>LSC-38</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D34" t="n">
-        <v>0.4566</v>
+        <v>0.37</v>
       </c>
       <c r="E34" t="n">
-        <v>0.8951</v>
+        <v>0.8358</v>
       </c>
       <c r="F34" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.219</v>
       </c>
       <c r="G34" t="n">
-        <v>0.8871</v>
+        <v>0.6169</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -1463,26 +1463,26 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>LSC-32</t>
+          <t>LSC-39</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D35" t="n">
-        <v>0.3339</v>
+        <v>0.1501</v>
       </c>
       <c r="E35" t="n">
-        <v>0.8862</v>
+        <v>0.8518</v>
       </c>
       <c r="F35" t="n">
-        <v>0.0207</v>
+        <v>0.1943</v>
       </c>
       <c r="G35" t="n">
-        <v>0.8655</v>
+        <v>0.6575</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -1493,26 +1493,26 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>LSC-37</t>
+          <t>LSC-40</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C36" t="n">
-        <v>0.988503117170494</v>
+        <v>0.066</v>
       </c>
       <c r="D36" t="n">
-        <v>0.4329</v>
+        <v>0.1091</v>
       </c>
       <c r="E36" t="n">
-        <v>0.8959</v>
+        <v>0.7989000000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>0.008</v>
+        <v>0.1406</v>
       </c>
       <c r="G36" t="n">
-        <v>0.888</v>
+        <v>0.6583</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -1523,26 +1523,26 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>LSC-38</t>
+          <t>LSC-41</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D37" t="n">
-        <v>0.3815</v>
+        <v>0.1515</v>
       </c>
       <c r="E37" t="n">
-        <v>0.8791</v>
+        <v>0.6942</v>
       </c>
       <c r="F37" t="n">
-        <v>0.013</v>
+        <v>0.289</v>
       </c>
       <c r="G37" t="n">
-        <v>0.8661</v>
+        <v>0.4052</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -1553,26 +1553,26 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>LSC-39</t>
+          <t>LSC-42</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C38" t="n">
-        <v>0.988503117170494</v>
+        <v>0.066</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1483</v>
+        <v>0.1154</v>
       </c>
       <c r="E38" t="n">
-        <v>0.8774</v>
+        <v>0.7715</v>
       </c>
       <c r="F38" t="n">
-        <v>0.0287</v>
+        <v>0.1434</v>
       </c>
       <c r="G38" t="n">
-        <v>0.8487</v>
+        <v>0.6281</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -1583,26 +1583,26 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>LSC-40</t>
+          <t>LSC-43</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>0.86598189210379</v>
+        <v>0.066</v>
       </c>
       <c r="D39" t="n">
-        <v>0.2377</v>
+        <v>0.1163</v>
       </c>
       <c r="E39" t="n">
-        <v>0.9488</v>
+        <v>0.7911</v>
       </c>
       <c r="F39" t="n">
-        <v>0.1226</v>
+        <v>0.1526</v>
       </c>
       <c r="G39" t="n">
-        <v>0.8262</v>
+        <v>0.6385999999999999</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -1613,26 +1613,26 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>LSC-41</t>
+          <t>LSC-45</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>1</v>
       </c>
       <c r="C40" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D40" t="n">
-        <v>0.1128</v>
+        <v>0.4243</v>
       </c>
       <c r="E40" t="n">
-        <v>0.7423</v>
+        <v>0.9214</v>
       </c>
       <c r="F40" t="n">
-        <v>0.1316</v>
+        <v>0.1121</v>
       </c>
       <c r="G40" t="n">
-        <v>0.6107</v>
+        <v>0.8093</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -1643,26 +1643,26 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>LSC-42</t>
+          <t>LSC-53</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C41" t="n">
-        <v>0.86598189210379</v>
+        <v>0.09</v>
       </c>
       <c r="D41" t="n">
-        <v>0.2019</v>
+        <v>0.4439</v>
       </c>
       <c r="E41" t="n">
-        <v>0.9246</v>
+        <v>0.9265</v>
       </c>
       <c r="F41" t="n">
-        <v>0.2076</v>
+        <v>0.1107</v>
       </c>
       <c r="G41" t="n">
-        <v>0.717</v>
+        <v>0.8158</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -1673,26 +1673,26 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>LSC-43</t>
+          <t>LSC-55</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>0.86598189210379</v>
+        <v>0.09</v>
       </c>
       <c r="D42" t="n">
-        <v>0.1666</v>
+        <v>0.2239</v>
       </c>
       <c r="E42" t="n">
-        <v>0.9446</v>
+        <v>0.7786</v>
       </c>
       <c r="F42" t="n">
-        <v>0.1399</v>
+        <v>0.2778</v>
       </c>
       <c r="G42" t="n">
-        <v>0.8047</v>
+        <v>0.5008</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -1703,26 +1703,26 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>LSC-45</t>
+          <t>LSC-56</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D43" t="n">
-        <v>0.3913</v>
+        <v>0.3934</v>
       </c>
       <c r="E43" t="n">
-        <v>0.8977000000000001</v>
+        <v>0.9231</v>
       </c>
       <c r="F43" t="n">
-        <v>0.0071</v>
+        <v>0.106</v>
       </c>
       <c r="G43" t="n">
-        <v>0.8905</v>
+        <v>0.8171</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -1733,26 +1733,26 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>LSC-47</t>
+          <t>LSC-57</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>2</v>
       </c>
       <c r="C44" t="n">
-        <v>0.86598189210379</v>
+        <v>0.066</v>
       </c>
       <c r="D44" t="n">
-        <v>0.1806</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="E44" t="n">
-        <v>0.9491000000000001</v>
+        <v>0.6025</v>
       </c>
       <c r="F44" t="n">
-        <v>0.1097</v>
+        <v>0.4327</v>
       </c>
       <c r="G44" t="n">
-        <v>0.8395</v>
+        <v>0.1698</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -1763,26 +1763,26 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>LSC-48</t>
+          <t>LSC-58</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>2</v>
       </c>
       <c r="C45" t="n">
-        <v>0.86598189210379</v>
+        <v>0.066</v>
       </c>
       <c r="D45" t="n">
-        <v>0.2716</v>
+        <v>-0.0721</v>
       </c>
       <c r="E45" t="n">
-        <v>0.9454</v>
+        <v>0.6968</v>
       </c>
       <c r="F45" t="n">
-        <v>0.1199</v>
+        <v>0.3101</v>
       </c>
       <c r="G45" t="n">
-        <v>0.8255</v>
+        <v>0.3867</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -1793,26 +1793,26 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>LSC-53</t>
+          <t>LSC-59</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C46" t="n">
-        <v>0.988503117170494</v>
+        <v>0.066</v>
       </c>
       <c r="D46" t="n">
-        <v>0.4014</v>
+        <v>0.1525</v>
       </c>
       <c r="E46" t="n">
-        <v>0.896</v>
+        <v>0.7981</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0074</v>
+        <v>0.1366</v>
       </c>
       <c r="G46" t="n">
-        <v>0.8885</v>
+        <v>0.6615</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -1823,26 +1823,26 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>LSC-55</t>
+          <t>LSC-60</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C47" t="n">
-        <v>0.988503117170494</v>
+        <v>0.066</v>
       </c>
       <c r="D47" t="n">
-        <v>0.2514</v>
+        <v>0.0504</v>
       </c>
       <c r="E47" t="n">
-        <v>0.8607</v>
+        <v>0.7685</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0281</v>
+        <v>0.1763</v>
       </c>
       <c r="G47" t="n">
-        <v>0.8326</v>
+        <v>0.5921999999999999</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -1853,26 +1853,26 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>LSC-56</t>
+          <t>LSC-62</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>1</v>
       </c>
       <c r="C48" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D48" t="n">
-        <v>0.3656</v>
+        <v>0.3807</v>
       </c>
       <c r="E48" t="n">
-        <v>0.8922</v>
+        <v>0.9232</v>
       </c>
       <c r="F48" t="n">
-        <v>0.008</v>
+        <v>0.1082</v>
       </c>
       <c r="G48" t="n">
-        <v>0.8842</v>
+        <v>0.8151</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -1883,26 +1883,26 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>LSC-57</t>
+          <t>SCR-08</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>1</v>
       </c>
       <c r="C49" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D49" t="n">
-        <v>0.1815</v>
+        <v>0.4603</v>
       </c>
       <c r="E49" t="n">
-        <v>0.6506999999999999</v>
+        <v>0.9218</v>
       </c>
       <c r="F49" t="n">
-        <v>0.3048</v>
+        <v>0.1081</v>
       </c>
       <c r="G49" t="n">
-        <v>0.346</v>
+        <v>0.8137</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -1913,26 +1913,26 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>LSC-58</t>
+          <t>DR-144</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>1</v>
       </c>
       <c r="C50" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D50" t="n">
-        <v>0.1796</v>
+        <v>0.3558</v>
       </c>
       <c r="E50" t="n">
-        <v>0.4981</v>
+        <v>0.9208</v>
       </c>
       <c r="F50" t="n">
-        <v>0.4785</v>
+        <v>0.113</v>
       </c>
       <c r="G50" t="n">
-        <v>0.0195</v>
+        <v>0.8078</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -1943,26 +1943,26 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>LSC-59</t>
+          <t>DR-145</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C51" t="n">
-        <v>0.86598189210379</v>
+        <v>0.09</v>
       </c>
       <c r="D51" t="n">
-        <v>0.2938</v>
+        <v>0.3277</v>
       </c>
       <c r="E51" t="n">
-        <v>0.9471000000000001</v>
+        <v>0.9234</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1215</v>
+        <v>0.1047</v>
       </c>
       <c r="G51" t="n">
-        <v>0.8256</v>
+        <v>0.8188</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -1973,26 +1973,26 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>LSC-60</t>
+          <t>SCR-09</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.0121</v>
+        <v>0.4018</v>
       </c>
       <c r="E52" t="n">
-        <v>0.3275</v>
+        <v>0.926</v>
       </c>
       <c r="F52" t="n">
-        <v>0.6505</v>
+        <v>0.1096</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.323</v>
+        <v>0.8164</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2003,238 +2003,28 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>LSC-62</t>
+          <t>DR-159</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>1</v>
       </c>
       <c r="C53" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D53" t="n">
-        <v>0.3733</v>
+        <v>0.3831</v>
       </c>
       <c r="E53" t="n">
-        <v>0.8964</v>
+        <v>0.9262</v>
       </c>
       <c r="F53" t="n">
-        <v>0.0067</v>
+        <v>0.1083</v>
       </c>
       <c r="G53" t="n">
-        <v>0.8897</v>
+        <v>0.8179</v>
       </c>
       <c r="H53" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t>SCR-08</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>1</v>
-      </c>
-      <c r="C54" t="n">
-        <v>0.988503117170494</v>
-      </c>
-      <c r="D54" t="n">
-        <v>0.4304</v>
-      </c>
-      <c r="E54" t="n">
-        <v>0.8959</v>
-      </c>
-      <c r="F54" t="n">
-        <v>0.0075</v>
-      </c>
-      <c r="G54" t="n">
-        <v>0.8884</v>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="inlineStr">
-        <is>
-          <t>DR-144</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>1</v>
-      </c>
-      <c r="C55" t="n">
-        <v>0.988503117170494</v>
-      </c>
-      <c r="D55" t="n">
-        <v>0.3627</v>
-      </c>
-      <c r="E55" t="n">
-        <v>0.8983</v>
-      </c>
-      <c r="F55" t="n">
-        <v>0.0064</v>
-      </c>
-      <c r="G55" t="n">
-        <v>0.8919</v>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="inlineStr">
-        <is>
-          <t>DR-145</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>1</v>
-      </c>
-      <c r="C56" t="n">
-        <v>0.988503117170494</v>
-      </c>
-      <c r="D56" t="n">
-        <v>0.2897</v>
-      </c>
-      <c r="E56" t="n">
-        <v>0.8925</v>
-      </c>
-      <c r="F56" t="n">
-        <v>0.0074</v>
-      </c>
-      <c r="G56" t="n">
-        <v>0.8851</v>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="inlineStr">
-        <is>
-          <t>SCR-09</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>1</v>
-      </c>
-      <c r="C57" t="n">
-        <v>0.988503117170494</v>
-      </c>
-      <c r="D57" t="n">
-        <v>0.4021</v>
-      </c>
-      <c r="E57" t="n">
-        <v>0.8931</v>
-      </c>
-      <c r="F57" t="n">
-        <v>0.0074</v>
-      </c>
-      <c r="G57" t="n">
-        <v>0.8857</v>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="1" t="inlineStr">
-        <is>
-          <t>DR-156</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>1</v>
-      </c>
-      <c r="C58" t="n">
-        <v>0.988503117170494</v>
-      </c>
-      <c r="D58" t="n">
-        <v>0.3886</v>
-      </c>
-      <c r="E58" t="n">
-        <v>0.8947000000000001</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0.0076</v>
-      </c>
-      <c r="G58" t="n">
-        <v>0.8871</v>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="1" t="inlineStr">
-        <is>
-          <t>DR-157</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>1</v>
-      </c>
-      <c r="C59" t="n">
-        <v>0.988503117170494</v>
-      </c>
-      <c r="D59" t="n">
-        <v>0.2416</v>
-      </c>
-      <c r="E59" t="n">
-        <v>0.8792</v>
-      </c>
-      <c r="F59" t="n">
-        <v>0.0237</v>
-      </c>
-      <c r="G59" t="n">
-        <v>0.8555</v>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="1" t="inlineStr">
-        <is>
-          <t>DR-159</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>1</v>
-      </c>
-      <c r="C60" t="n">
-        <v>0.988503117170494</v>
-      </c>
-      <c r="D60" t="n">
-        <v>0.3091</v>
-      </c>
-      <c r="E60" t="n">
-        <v>0.8944</v>
-      </c>
-      <c r="F60" t="n">
-        <v>0.0076</v>
-      </c>
-      <c r="G60" t="n">
-        <v>0.8868</v>
-      </c>
-      <c r="H60" t="inlineStr">
         <is>
           <t>Core</t>
         </is>

--- a/results/02_taxa_assemblage/WardsClustering/tables/taxa_confidence/site_robustness.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/tables/taxa_confidence/site_robustness.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,19 +480,19 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3081</v>
+        <v>0.3202</v>
       </c>
       <c r="E2" t="n">
-        <v>0.918</v>
+        <v>0.8939</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1096</v>
+        <v>0.0074</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8084</v>
+        <v>0.8865</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,19 +510,19 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1713</v>
+        <v>0.2267</v>
       </c>
       <c r="E3" t="n">
-        <v>0.755</v>
+        <v>0.8777</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3102</v>
+        <v>0.0303</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4449</v>
+        <v>0.8474</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -537,22 +537,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>0.066</v>
+        <v>0.940958804337006</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1649</v>
+        <v>-0.0713</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8179</v>
+        <v>0.7866</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1318</v>
+        <v>0.3453</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6861</v>
+        <v>0.4413</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -570,19 +570,19 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3696</v>
+        <v>0.2942</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9246</v>
+        <v>0.895</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1079</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8168</v>
+        <v>0.8867</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -600,19 +600,19 @@
         <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>0.870534508464975</v>
+        <v>0.940958804337006</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1837</v>
+        <v>0.1115</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8568</v>
+        <v>0.8725000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1485</v>
+        <v>0.0898</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7083</v>
+        <v>0.7827</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -627,22 +627,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>0.066</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D7" t="n">
-        <v>0.09039999999999999</v>
+        <v>-0.1004</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8075</v>
+        <v>0.2041</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1323</v>
+        <v>0.7847</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6753</v>
+        <v>-0.5806</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -660,19 +660,19 @@
         <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>0.870534508464975</v>
+        <v>0.940958804337006</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1285</v>
+        <v>0.1032</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7402</v>
+        <v>0.9091</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2036</v>
+        <v>0.161</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5366</v>
+        <v>0.7481</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -690,19 +690,19 @@
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1088</v>
+        <v>0.2234</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6993</v>
+        <v>0.8088</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3244</v>
+        <v>0.0672</v>
       </c>
       <c r="G9" t="n">
-        <v>0.375</v>
+        <v>0.7416</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -717,22 +717,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>0.066</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.09080000000000001</v>
+        <v>0.1956</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3674</v>
+        <v>0.7721</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6168</v>
+        <v>0.1134</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2494</v>
+        <v>0.6587</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -750,19 +750,19 @@
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4638</v>
+        <v>0.444</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9247</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>0.111</v>
+        <v>0.0075</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8136</v>
+        <v>0.8872</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -780,19 +780,19 @@
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4503</v>
+        <v>0.4431</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9255</v>
+        <v>0.8972</v>
       </c>
       <c r="F12" t="n">
-        <v>0.107</v>
+        <v>0.0073</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8185</v>
+        <v>0.89</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -803,26 +803,26 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>DR-143</t>
+          <t>DR-141</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>0.066</v>
+        <v>0.940958804337006</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0164</v>
+        <v>0.1635</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5613</v>
+        <v>0.9241</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3262</v>
+        <v>0.1859</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2351</v>
+        <v>0.7382</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -833,26 +833,26 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>SCR-11</t>
+          <t>DR-143</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>0.09</v>
+        <v>0.86598189210379</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4816</v>
+        <v>0.0428</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9231</v>
+        <v>0.7708</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1101</v>
+        <v>0.3052</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.4656</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -863,26 +863,26 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>SCR-14</t>
+          <t>SCR-11</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2649</v>
+        <v>0.449</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9248</v>
+        <v>0.8937</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1166</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8082</v>
+        <v>0.8858</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -893,26 +893,26 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>SCR-17</t>
+          <t>SCR-14</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>0.870534508464975</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1831</v>
+        <v>0.2812</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8425</v>
+        <v>0.8942</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1477</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6948</v>
+        <v>0.8861</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -923,26 +923,26 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>SCR-18</t>
+          <t>SCR-17</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>0.09</v>
+        <v>0.940958804337006</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3454</v>
+        <v>0.1556</v>
       </c>
       <c r="E17" t="n">
-        <v>0.926</v>
+        <v>0.9142</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1128</v>
+        <v>0.1014</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8132</v>
+        <v>0.8128</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -953,26 +953,26 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>SCR-19</t>
+          <t>SCR-18</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>0.870534508464975</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3525</v>
+        <v>0.3595</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8466</v>
+        <v>0.8949</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0456</v>
+        <v>0.008</v>
       </c>
       <c r="G18" t="n">
-        <v>0.801</v>
+        <v>0.8869</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -983,26 +983,26 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>SCR-20</t>
+          <t>SCR-19</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>0.09</v>
+        <v>0.940958804337006</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2344</v>
+        <v>0.3168</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8711</v>
+        <v>0.9093</v>
       </c>
       <c r="F19" t="n">
-        <v>0.145</v>
+        <v>0.0496</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7261</v>
+        <v>0.8597</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1013,26 +1013,26 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>LSC-14</t>
+          <t>SCR-20</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1969</v>
+        <v>0.2357</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7502</v>
+        <v>0.8474</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2754</v>
+        <v>0.0323</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4748</v>
+        <v>0.8151</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1043,26 +1043,26 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>LSC-15</t>
+          <t>LSC-14</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D21" t="n">
-        <v>0.208</v>
+        <v>0.1873</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7749</v>
+        <v>0.7983</v>
       </c>
       <c r="F21" t="n">
-        <v>0.264</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5109</v>
+        <v>0.7060999999999999</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1073,26 +1073,26 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>LSC-16</t>
+          <t>LSC-15</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4761</v>
+        <v>0.221</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9179</v>
+        <v>0.8221000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1049</v>
+        <v>0.0599</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8131</v>
+        <v>0.7623</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1103,26 +1103,26 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>LSC-17</t>
+          <t>LSC-16</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4605</v>
+        <v>0.4601</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9241</v>
+        <v>0.8948</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1074</v>
+        <v>0.0071</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8167</v>
+        <v>0.8877</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1133,26 +1133,26 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>LSC-18</t>
+          <t>LSC-17</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2554</v>
+        <v>0.4298</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9127999999999999</v>
+        <v>0.8957000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>0.118</v>
+        <v>0.0077</v>
       </c>
       <c r="G24" t="n">
-        <v>0.7948</v>
+        <v>0.8879</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1163,26 +1163,26 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>LSC-19</t>
+          <t>LSC-18</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4989</v>
+        <v>0.2427</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9221</v>
+        <v>0.8931</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1073</v>
+        <v>0.0083</v>
       </c>
       <c r="G25" t="n">
-        <v>0.8148</v>
+        <v>0.8848</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1193,26 +1193,26 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>LSC-22</t>
+          <t>LSC-19</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3386</v>
+        <v>0.4728</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8368</v>
+        <v>0.8951</v>
       </c>
       <c r="F26" t="n">
-        <v>0.218</v>
+        <v>0.0065</v>
       </c>
       <c r="G26" t="n">
-        <v>0.6188</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1223,26 +1223,26 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>LSC-23</t>
+          <t>LSC-22</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>0.066</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D27" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.3781</v>
       </c>
       <c r="E27" t="n">
-        <v>0.8027</v>
+        <v>0.8758</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1378</v>
+        <v>0.0155</v>
       </c>
       <c r="G27" t="n">
-        <v>0.6649</v>
+        <v>0.8602</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1253,26 +1253,26 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>LSC-24</t>
+          <t>LSC-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>0.09</v>
+        <v>0.86598189210379</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4497</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>0.9219000000000001</v>
+        <v>0.9004</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1022</v>
+        <v>0.1176</v>
       </c>
       <c r="G28" t="n">
-        <v>0.8197</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1283,26 +1283,26 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>LSC-25</t>
+          <t>LSC-24</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3727</v>
+        <v>0.4393</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9131</v>
+        <v>0.8939</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1236</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="G29" t="n">
-        <v>0.7895</v>
+        <v>0.8856000000000001</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1313,26 +1313,26 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>LSC-26</t>
+          <t>LSC-25</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D30" t="n">
-        <v>0.4094</v>
+        <v>0.3796</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9155</v>
+        <v>0.891</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1222</v>
+        <v>0.01</v>
       </c>
       <c r="G30" t="n">
-        <v>0.7933</v>
+        <v>0.8809</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1343,26 +1343,26 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>LSC-27</t>
+          <t>LSC-26</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3314</v>
+        <v>0.3991</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9214</v>
+        <v>0.8956</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1147</v>
+        <v>0.0086</v>
       </c>
       <c r="G31" t="n">
-        <v>0.8067</v>
+        <v>0.887</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1373,26 +1373,26 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>SCR-06</t>
+          <t>LSC-27</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>0.870534508464975</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.1492</v>
+        <v>0.3534</v>
       </c>
       <c r="E32" t="n">
-        <v>0.5443</v>
+        <v>0.8966</v>
       </c>
       <c r="F32" t="n">
-        <v>0.368</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="G32" t="n">
-        <v>0.1763</v>
+        <v>0.8873</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -1403,26 +1403,26 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>LSC-37</t>
+          <t>SCR-06</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D33" t="n">
-        <v>0.4694</v>
+        <v>0.1775</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9225</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1061</v>
+        <v>0.3974</v>
       </c>
       <c r="G33" t="n">
-        <v>0.8164</v>
+        <v>0.1103</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -1433,26 +1433,26 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>LSC-38</t>
+          <t>LSC-30</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D34" t="n">
-        <v>0.37</v>
+        <v>0.4566</v>
       </c>
       <c r="E34" t="n">
-        <v>0.8358</v>
+        <v>0.8951</v>
       </c>
       <c r="F34" t="n">
-        <v>0.219</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="G34" t="n">
-        <v>0.6169</v>
+        <v>0.8871</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -1463,26 +1463,26 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>LSC-39</t>
+          <t>LSC-32</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1501</v>
+        <v>0.3339</v>
       </c>
       <c r="E35" t="n">
-        <v>0.8518</v>
+        <v>0.8862</v>
       </c>
       <c r="F35" t="n">
-        <v>0.1943</v>
+        <v>0.0207</v>
       </c>
       <c r="G35" t="n">
-        <v>0.6575</v>
+        <v>0.8655</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -1493,26 +1493,26 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>LSC-40</t>
+          <t>LSC-37</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>0.066</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1091</v>
+        <v>0.4329</v>
       </c>
       <c r="E36" t="n">
-        <v>0.7989000000000001</v>
+        <v>0.8959</v>
       </c>
       <c r="F36" t="n">
-        <v>0.1406</v>
+        <v>0.008</v>
       </c>
       <c r="G36" t="n">
-        <v>0.6583</v>
+        <v>0.888</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -1523,26 +1523,26 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>LSC-41</t>
+          <t>LSC-38</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1515</v>
+        <v>0.3815</v>
       </c>
       <c r="E37" t="n">
-        <v>0.6942</v>
+        <v>0.8791</v>
       </c>
       <c r="F37" t="n">
-        <v>0.289</v>
+        <v>0.013</v>
       </c>
       <c r="G37" t="n">
-        <v>0.4052</v>
+        <v>0.8661</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -1553,26 +1553,26 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>LSC-42</t>
+          <t>LSC-39</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C38" t="n">
-        <v>0.066</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1154</v>
+        <v>0.1483</v>
       </c>
       <c r="E38" t="n">
-        <v>0.7715</v>
+        <v>0.8774</v>
       </c>
       <c r="F38" t="n">
-        <v>0.1434</v>
+        <v>0.0287</v>
       </c>
       <c r="G38" t="n">
-        <v>0.6281</v>
+        <v>0.8487</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -1583,26 +1583,26 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>LSC-43</t>
+          <t>LSC-40</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>0.066</v>
+        <v>0.86598189210379</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1163</v>
+        <v>0.2377</v>
       </c>
       <c r="E39" t="n">
-        <v>0.7911</v>
+        <v>0.9488</v>
       </c>
       <c r="F39" t="n">
-        <v>0.1526</v>
+        <v>0.1226</v>
       </c>
       <c r="G39" t="n">
-        <v>0.6385999999999999</v>
+        <v>0.8262</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -1613,26 +1613,26 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>LSC-45</t>
+          <t>LSC-41</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>1</v>
       </c>
       <c r="C40" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D40" t="n">
-        <v>0.4243</v>
+        <v>0.1128</v>
       </c>
       <c r="E40" t="n">
-        <v>0.9214</v>
+        <v>0.7423</v>
       </c>
       <c r="F40" t="n">
-        <v>0.1121</v>
+        <v>0.1316</v>
       </c>
       <c r="G40" t="n">
-        <v>0.8093</v>
+        <v>0.6107</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -1643,26 +1643,26 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>LSC-53</t>
+          <t>LSC-42</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>0.09</v>
+        <v>0.86598189210379</v>
       </c>
       <c r="D41" t="n">
-        <v>0.4439</v>
+        <v>0.2019</v>
       </c>
       <c r="E41" t="n">
-        <v>0.9265</v>
+        <v>0.9246</v>
       </c>
       <c r="F41" t="n">
-        <v>0.1107</v>
+        <v>0.2076</v>
       </c>
       <c r="G41" t="n">
-        <v>0.8158</v>
+        <v>0.717</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -1673,26 +1673,26 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>LSC-55</t>
+          <t>LSC-43</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C42" t="n">
-        <v>0.09</v>
+        <v>0.86598189210379</v>
       </c>
       <c r="D42" t="n">
-        <v>0.2239</v>
+        <v>0.1666</v>
       </c>
       <c r="E42" t="n">
-        <v>0.7786</v>
+        <v>0.9446</v>
       </c>
       <c r="F42" t="n">
-        <v>0.2778</v>
+        <v>0.1399</v>
       </c>
       <c r="G42" t="n">
-        <v>0.5008</v>
+        <v>0.8047</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -1703,26 +1703,26 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>LSC-56</t>
+          <t>LSC-45</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D43" t="n">
-        <v>0.3934</v>
+        <v>0.3913</v>
       </c>
       <c r="E43" t="n">
-        <v>0.9231</v>
+        <v>0.8977000000000001</v>
       </c>
       <c r="F43" t="n">
-        <v>0.106</v>
+        <v>0.0071</v>
       </c>
       <c r="G43" t="n">
-        <v>0.8171</v>
+        <v>0.8905</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -1733,26 +1733,26 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>LSC-57</t>
+          <t>LSC-47</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>2</v>
       </c>
       <c r="C44" t="n">
-        <v>0.066</v>
+        <v>0.86598189210379</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.08599999999999999</v>
+        <v>0.1806</v>
       </c>
       <c r="E44" t="n">
-        <v>0.6025</v>
+        <v>0.9491000000000001</v>
       </c>
       <c r="F44" t="n">
-        <v>0.4327</v>
+        <v>0.1097</v>
       </c>
       <c r="G44" t="n">
-        <v>0.1698</v>
+        <v>0.8395</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -1763,26 +1763,26 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>LSC-58</t>
+          <t>LSC-48</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>2</v>
       </c>
       <c r="C45" t="n">
-        <v>0.066</v>
+        <v>0.86598189210379</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.0721</v>
+        <v>0.2716</v>
       </c>
       <c r="E45" t="n">
-        <v>0.6968</v>
+        <v>0.9454</v>
       </c>
       <c r="F45" t="n">
-        <v>0.3101</v>
+        <v>0.1199</v>
       </c>
       <c r="G45" t="n">
-        <v>0.3867</v>
+        <v>0.8255</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -1793,26 +1793,26 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>LSC-59</t>
+          <t>LSC-53</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>0.066</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D46" t="n">
-        <v>0.1525</v>
+        <v>0.4014</v>
       </c>
       <c r="E46" t="n">
-        <v>0.7981</v>
+        <v>0.896</v>
       </c>
       <c r="F46" t="n">
-        <v>0.1366</v>
+        <v>0.0074</v>
       </c>
       <c r="G46" t="n">
-        <v>0.6615</v>
+        <v>0.8885</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -1823,26 +1823,26 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>LSC-60</t>
+          <t>LSC-55</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C47" t="n">
-        <v>0.066</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0504</v>
+        <v>0.2514</v>
       </c>
       <c r="E47" t="n">
-        <v>0.7685</v>
+        <v>0.8607</v>
       </c>
       <c r="F47" t="n">
-        <v>0.1763</v>
+        <v>0.0281</v>
       </c>
       <c r="G47" t="n">
-        <v>0.5921999999999999</v>
+        <v>0.8326</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -1853,26 +1853,26 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>LSC-62</t>
+          <t>LSC-56</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>1</v>
       </c>
       <c r="C48" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D48" t="n">
-        <v>0.3807</v>
+        <v>0.3656</v>
       </c>
       <c r="E48" t="n">
-        <v>0.9232</v>
+        <v>0.8922</v>
       </c>
       <c r="F48" t="n">
-        <v>0.1082</v>
+        <v>0.008</v>
       </c>
       <c r="G48" t="n">
-        <v>0.8151</v>
+        <v>0.8842</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -1883,26 +1883,26 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>SCR-08</t>
+          <t>LSC-57</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>1</v>
       </c>
       <c r="C49" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D49" t="n">
-        <v>0.4603</v>
+        <v>0.1815</v>
       </c>
       <c r="E49" t="n">
-        <v>0.9218</v>
+        <v>0.6506999999999999</v>
       </c>
       <c r="F49" t="n">
-        <v>0.1081</v>
+        <v>0.3048</v>
       </c>
       <c r="G49" t="n">
-        <v>0.8137</v>
+        <v>0.346</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -1913,26 +1913,26 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>DR-144</t>
+          <t>LSC-58</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>1</v>
       </c>
       <c r="C50" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D50" t="n">
-        <v>0.3558</v>
+        <v>0.1796</v>
       </c>
       <c r="E50" t="n">
-        <v>0.9208</v>
+        <v>0.4981</v>
       </c>
       <c r="F50" t="n">
-        <v>0.113</v>
+        <v>0.4785</v>
       </c>
       <c r="G50" t="n">
-        <v>0.8078</v>
+        <v>0.0195</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -1943,26 +1943,26 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>DR-145</t>
+          <t>LSC-59</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C51" t="n">
-        <v>0.09</v>
+        <v>0.86598189210379</v>
       </c>
       <c r="D51" t="n">
-        <v>0.3277</v>
+        <v>0.2938</v>
       </c>
       <c r="E51" t="n">
-        <v>0.9234</v>
+        <v>0.9471000000000001</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1047</v>
+        <v>0.1215</v>
       </c>
       <c r="G51" t="n">
-        <v>0.8188</v>
+        <v>0.8256</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -1973,26 +1973,26 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>SCR-09</t>
+          <t>LSC-60</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D52" t="n">
-        <v>0.4018</v>
+        <v>-0.0121</v>
       </c>
       <c r="E52" t="n">
-        <v>0.926</v>
+        <v>0.3275</v>
       </c>
       <c r="F52" t="n">
-        <v>0.1096</v>
+        <v>0.6505</v>
       </c>
       <c r="G52" t="n">
-        <v>0.8164</v>
+        <v>-0.323</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2003,28 +2003,238 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
+          <t>LSC-62</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.988503117170494</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.3733</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.8964</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.0067</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.8897</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>SCR-08</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.988503117170494</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.4304</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.8959</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.8884</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>DR-144</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.988503117170494</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.8983</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.0064</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.8919</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>DR-145</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.988503117170494</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.2897</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.8925</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.0074</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.8851</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>SCR-09</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.988503117170494</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0.4021</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.8931</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.0074</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.8857</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>DR-156</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.988503117170494</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.3886</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.8947000000000001</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.8871</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>DR-157</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.988503117170494</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.2416</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.8792</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.0237</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.8555</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
           <t>DR-159</t>
         </is>
       </c>
-      <c r="B53" t="n">
-        <v>1</v>
-      </c>
-      <c r="C53" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="D53" t="n">
-        <v>0.3831</v>
-      </c>
-      <c r="E53" t="n">
-        <v>0.9262</v>
-      </c>
-      <c r="F53" t="n">
-        <v>0.1083</v>
-      </c>
-      <c r="G53" t="n">
-        <v>0.8179</v>
-      </c>
-      <c r="H53" t="inlineStr">
+      <c r="B60" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.988503117170494</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.8944</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.8868</v>
+      </c>
+      <c r="H60" t="inlineStr">
         <is>
           <t>Core</t>
         </is>
